--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_104_R11.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_104_R11.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>W. TAVARES</t>
+          <t>A. FELIZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.3594</v>
+        <v>4.5071</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0617</v>
+        <v>5.0796</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.7023</v>
+        <v>-0.5725</v>
       </c>
       <c r="G2" t="n">
-        <v>1.1739</v>
+        <v>3.7878</v>
       </c>
       <c r="H2" t="n">
-        <v>2.0838</v>
+        <v>2.4427</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.9099</v>
+        <v>1.3451</v>
       </c>
       <c r="J2" t="n">
-        <v>2.843</v>
+        <v>5.2641</v>
       </c>
       <c r="K2" t="n">
-        <v>2.6958</v>
+        <v>3.1796</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1472</v>
+        <v>2.0844</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.6691</v>
+        <v>-1.4762</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.612</v>
+        <v>-0.7369</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.0572</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.232</v>
+        <v>0.9278</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0.9278</v>
       </c>
       <c r="S2" t="n">
-        <v>3.3453</v>
+        <v>-0.0668</v>
       </c>
       <c r="T2" t="n">
-        <v>1.9505</v>
+        <v>-0.1845</v>
       </c>
       <c r="U2" t="n">
-        <v>1.3948</v>
+        <v>0.1177</v>
       </c>
       <c r="V2" t="n">
-        <v>1.0722</v>
+        <v>-0.1418</v>
       </c>
       <c r="W2" t="n">
-        <v>2.428</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.3558</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. FELIZ</t>
+          <t>W. TAVARES</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.5071</v>
+        <v>3.2712</v>
       </c>
       <c r="E3" t="n">
-        <v>5.0796</v>
+        <v>4.4104</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5725</v>
+        <v>-1.1392</v>
       </c>
       <c r="G3" t="n">
-        <v>3.7878</v>
+        <v>1.1739</v>
       </c>
       <c r="H3" t="n">
-        <v>2.4427</v>
+        <v>2.0838</v>
       </c>
       <c r="I3" t="n">
-        <v>1.3451</v>
+        <v>-0.9099</v>
       </c>
       <c r="J3" t="n">
-        <v>5.2641</v>
+        <v>2.843</v>
       </c>
       <c r="K3" t="n">
-        <v>3.1796</v>
+        <v>2.6958</v>
       </c>
       <c r="L3" t="n">
-        <v>2.0844</v>
+        <v>0.1472</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.4762</v>
+        <v>-1.6691</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7369</v>
+        <v>-0.612</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.7393999999999999</v>
+        <v>-1.0572</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9278</v>
+        <v>-0.232</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R3" t="n">
         <v>0.9278</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0668</v>
+        <v>1.2571</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1845</v>
+        <v>0.2992</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1177</v>
+        <v>0.9579</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.1418</v>
+        <v>1.0722</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.428</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1418</v>
+        <v>-1.3558</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. OKEKE</t>
+          <t>A. ABALDE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4355</v>
+        <v>1.986</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1165</v>
+        <v>1.9105</v>
       </c>
       <c r="F4" t="n">
-        <v>1.319</v>
+        <v>0.0755</v>
       </c>
       <c r="G4" t="n">
-        <v>1.3368</v>
+        <v>2.4739</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1655</v>
+        <v>0.299</v>
       </c>
       <c r="I4" t="n">
-        <v>1.5023</v>
+        <v>2.1749</v>
       </c>
       <c r="J4" t="n">
-        <v>1.3836</v>
+        <v>1.9024</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4033</v>
+        <v>0.4068</v>
       </c>
       <c r="L4" t="n">
-        <v>0.9802999999999999</v>
+        <v>1.4956</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0468</v>
+        <v>0.5715</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5688</v>
+        <v>-0.1078</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5221</v>
+        <v>0.6793</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>0.4639</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3306</v>
+        <v>0.6565</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0351</v>
+        <v>0.0081</v>
       </c>
       <c r="U4" t="n">
-        <v>1.3658</v>
+        <v>0.6484</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. ABALDE</t>
+          <t>C. OKEKE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7336</v>
+        <v>1.9314</v>
       </c>
       <c r="E5" t="n">
-        <v>1.7925</v>
+        <v>1.1165</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0589</v>
+        <v>0.8149</v>
       </c>
       <c r="G5" t="n">
-        <v>2.4739</v>
+        <v>1.3368</v>
       </c>
       <c r="H5" t="n">
-        <v>0.299</v>
+        <v>-0.1655</v>
       </c>
       <c r="I5" t="n">
-        <v>2.1749</v>
+        <v>1.5023</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9024</v>
+        <v>1.3836</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4068</v>
+        <v>0.4033</v>
       </c>
       <c r="L5" t="n">
-        <v>1.4956</v>
+        <v>0.9802999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5715</v>
+        <v>-0.0468</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1078</v>
+        <v>-0.5688</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6793</v>
+        <v>0.5221</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4639</v>
+        <v>-0.232</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4639</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4042</v>
+        <v>0.8265</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1098</v>
+        <v>-0.0351</v>
       </c>
       <c r="U5" t="n">
-        <v>0.514</v>
+        <v>0.8617</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4101</v>
+        <v>-1.0506</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3292</v>
+        <v>-1.0369</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0809</v>
+        <v>-0.0137</v>
       </c>
       <c r="G6" t="n">
         <v>-1.4014</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.0789</v>
+        <v>0.4384</v>
       </c>
       <c r="T6" t="n">
-        <v>1.274</v>
+        <v>0.5663</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.195</v>
+        <v>-0.1278</v>
       </c>
       <c r="V6" t="n">
         <v>1.0722</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0394</v>
+        <v>-1.2417</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5149</v>
+        <v>-0.7508</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5245</v>
+        <v>-0.4909</v>
       </c>
       <c r="G7" t="n">
         <v>-0.2992</v>
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6515</v>
+        <v>0.4492</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7863</v>
+        <v>0.5504</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1349</v>
+        <v>-0.1013</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.9409</v>
+        <v>-1.5369</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.038</v>
+        <v>0.1979</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.9029</v>
+        <v>-1.7348</v>
       </c>
       <c r="G8" t="n">
         <v>-0.7645999999999999</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1278</v>
+        <v>0.5318000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0395</v>
+        <v>0.2754</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0883</v>
+        <v>0.2563</v>
       </c>
       <c r="V8" t="n">
         <v>-1.0722</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.7509</v>
+        <v>-2.2455</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3115</v>
+        <v>-0.8397</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.4394</v>
+        <v>-1.4058</v>
       </c>
       <c r="G9" t="n">
         <v>-2.2347</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2842</v>
+        <v>0.2212</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1494</v>
+        <v>0.3224</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1349</v>
+        <v>-0.1013</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.0276</v>
+        <v>-2.3542</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.3849</v>
+        <v>-0.9131</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.6427</v>
+        <v>-1.4411</v>
       </c>
       <c r="G10" t="n">
         <v>-2.3944</v>
@@ -1234,13 +1234,13 @@
         <v>0.4639</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0095</v>
+        <v>-0.3361</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6721</v>
+        <v>-0.2003</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3374</v>
+        <v>-0.1357</v>
       </c>
       <c r="V10" t="n">
         <v>1.0722</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.2337</v>
+        <v>-2.864</v>
       </c>
       <c r="E11" t="n">
         <v>-2.0171</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2165</v>
+        <v>-0.8469</v>
       </c>
       <c r="G11" t="n">
         <v>0.2692</v>
@@ -1312,13 +1312,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1208</v>
+        <v>0.4905</v>
       </c>
       <c r="T11" t="n">
         <v>0.0395</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0813</v>
+        <v>0.4509</v>
       </c>
       <c r="V11" t="n">
         <v>-1.0722</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.0688</v>
+        <v>-3.8899</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.1113</v>
+        <v>-3.1677</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.9575</v>
+        <v>-0.7223000000000001</v>
       </c>
       <c r="G12" t="n">
         <v>-4.927</v>
@@ -1390,13 +1390,13 @@
         <v>0.9278</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.3763</v>
+        <v>-0.1975</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.1949</v>
+        <v>-0.2513</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1814</v>
+        <v>0.0538</v>
       </c>
       <c r="V12" t="n">
         <v>1.4665</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.149</v>
+        <v>-6.0976</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.1934</v>
+        <v>-2.8395</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.9556</v>
+        <v>-3.2581</v>
       </c>
       <c r="G13" t="n">
         <v>-6.3129</v>
@@ -1468,13 +1468,13 @@
         <v>0.9278</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3958</v>
+        <v>0.4472</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1098</v>
+        <v>0.244</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5056</v>
+        <v>0.2032</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-9.584800000000001</v>
+        <v>-9.584700000000002</v>
       </c>
       <c r="E14" t="n">
-        <v>1.149999999999999</v>
+        <v>1.150099999999998</v>
       </c>
       <c r="F14" t="n">
-        <v>-10.7347</v>
+        <v>-10.7349</v>
       </c>
       <c r="G14" t="n">
         <v>-9.2926</v>
@@ -1546,13 +1546,13 @@
         <v>4.638999999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>4.718099999999999</v>
+        <v>4.718</v>
       </c>
       <c r="T14" t="n">
-        <v>1.634199999999999</v>
+        <v>1.6341</v>
       </c>
       <c r="U14" t="n">
-        <v>3.0839</v>
+        <v>3.0838</v>
       </c>
       <c r="V14" t="n">
         <v>0.7885999999999999</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>K. FARIED</t>
+          <t>T. SHORTS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.0382</v>
+        <v>5.5268</v>
       </c>
       <c r="E15" t="n">
-        <v>6.0244</v>
+        <v>4.6787</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.9862</v>
+        <v>0.8481</v>
       </c>
       <c r="G15" t="n">
-        <v>2.1212</v>
+        <v>3.3295</v>
       </c>
       <c r="H15" t="n">
-        <v>2.4992</v>
+        <v>1.2483</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.378</v>
+        <v>2.0812</v>
       </c>
       <c r="J15" t="n">
-        <v>2.7181</v>
+        <v>3.7588</v>
       </c>
       <c r="K15" t="n">
-        <v>2.4605</v>
+        <v>1.7246</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2576</v>
+        <v>2.0342</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.5969</v>
+        <v>-0.4293</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0387</v>
+        <v>-0.4762</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6356000000000001</v>
+        <v>0.047</v>
       </c>
       <c r="P15" t="n">
-        <v>1.3917</v>
+        <v>0.6959</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3917</v>
+        <v>1.8556</v>
       </c>
       <c r="S15" t="n">
-        <v>2.4557</v>
+        <v>-0.2486</v>
       </c>
       <c r="T15" t="n">
-        <v>1.9505</v>
+        <v>-0.7426</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5052</v>
+        <v>0.494</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.9304</v>
+        <v>1.7501</v>
       </c>
       <c r="W15" t="n">
-        <v>1.3558</v>
+        <v>2.8223</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.2862</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>T. SHORTS</t>
+          <t>K. FARIED</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.7347</v>
+        <v>3.4376</v>
       </c>
       <c r="E16" t="n">
-        <v>3.853</v>
+        <v>4.491</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8817</v>
+        <v>-1.0534</v>
       </c>
       <c r="G16" t="n">
-        <v>3.3295</v>
+        <v>2.1212</v>
       </c>
       <c r="H16" t="n">
-        <v>1.2483</v>
+        <v>2.4992</v>
       </c>
       <c r="I16" t="n">
-        <v>2.0812</v>
+        <v>-0.378</v>
       </c>
       <c r="J16" t="n">
-        <v>3.7588</v>
+        <v>2.7181</v>
       </c>
       <c r="K16" t="n">
-        <v>1.7246</v>
+        <v>2.4605</v>
       </c>
       <c r="L16" t="n">
-        <v>2.0342</v>
+        <v>0.2576</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4293</v>
+        <v>-0.5969</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4762</v>
+        <v>0.0387</v>
       </c>
       <c r="O16" t="n">
-        <v>0.047</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6959</v>
+        <v>1.3917</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8556</v>
+        <v>1.3917</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.0407</v>
+        <v>0.8551</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.5683</v>
+        <v>0.4171</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5276</v>
+        <v>0.438</v>
       </c>
       <c r="V16" t="n">
-        <v>1.7501</v>
+        <v>-0.9304</v>
       </c>
       <c r="W16" t="n">
-        <v>2.8223</v>
+        <v>1.3558</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.0722</v>
+        <v>-2.2862</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4172</v>
+        <v>2.6188</v>
       </c>
       <c r="E17" t="n">
         <v>2.7143</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2971</v>
+        <v>-0.0954</v>
       </c>
       <c r="G17" t="n">
         <v>3.9194</v>
@@ -1780,13 +1780,13 @@
         <v>1.3917</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.3399</v>
+        <v>-1.1382</v>
       </c>
       <c r="T17" t="n">
         <v>-0.3339</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.006</v>
+        <v>-0.8043</v>
       </c>
       <c r="V17" t="n">
         <v>-0.3943</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.5022</v>
+        <v>2.1256</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6312</v>
+        <v>2.2209</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1289</v>
+        <v>-0.0953</v>
       </c>
       <c r="G18" t="n">
         <v>1.1196</v>
@@ -1858,13 +1858,13 @@
         <v>1.1598</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.7076</v>
+        <v>-1.0842</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7468</v>
+        <v>-0.1571</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.9607</v>
+        <v>-0.9271</v>
       </c>
       <c r="V18" t="n">
         <v>0.9304</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6559</v>
+        <v>0.8747</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3099</v>
+        <v>0.4278</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3461</v>
+        <v>0.4469</v>
       </c>
       <c r="G19" t="n">
         <v>0.3489</v>
@@ -1936,13 +1936,13 @@
         <v>0.9278</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6207</v>
+        <v>-0.402</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7468</v>
+        <v>-0.6289</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1261</v>
+        <v>0.2269</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. GRANT</t>
+          <t>K. NUNN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3564</v>
+        <v>0.1696</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>-0.298</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3564</v>
+        <v>0.4677</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.2216</v>
+        <v>2.4951</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0108</v>
+        <v>-0.5197000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2108</v>
+        <v>3.0147</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>2.6385</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>-0.3795</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>3.018</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.2216</v>
+        <v>-0.1434</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0108</v>
+        <v>-0.1401</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2108</v>
+        <v>-0.0033</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>0.9278</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1349</v>
+        <v>-0.9337</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>-0.617</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1349</v>
+        <v>-0.3167</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. HERNANGOMEZ</t>
+          <t>J. GRANT</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5515</v>
+        <v>-0.3228</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.4933</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9418</v>
+        <v>-0.3228</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.2555</v>
+        <v>-0.2216</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6785</v>
+        <v>-0.0108</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.9341</v>
+        <v>-0.2108</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.423</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5581</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.9811</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1675</v>
+        <v>-0.2216</v>
       </c>
       <c r="N21" t="n">
-        <v>0.1205</v>
+        <v>-0.0108</v>
       </c>
       <c r="O21" t="n">
-        <v>0.047</v>
+        <v>-0.2108</v>
       </c>
       <c r="P21" t="n">
-        <v>1.6237</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.6237</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>1.2248</v>
+        <v>-0.1013</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0703</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.2951</v>
+        <v>-0.1013</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.1444</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.1444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>K. NUNN</t>
+          <t>A. SAMODUROV</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.6546999999999999</v>
+        <v>-0.887</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.6519</v>
+        <v>-0.6148</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0028</v>
+        <v>-0.2722</v>
       </c>
       <c r="G22" t="n">
-        <v>2.4951</v>
+        <v>-0.997</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.5197000000000001</v>
+        <v>0.1741</v>
       </c>
       <c r="I22" t="n">
-        <v>3.0147</v>
+        <v>-1.1711</v>
       </c>
       <c r="J22" t="n">
-        <v>2.6385</v>
+        <v>-0.7327</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.3795</v>
+        <v>0.0168</v>
       </c>
       <c r="L22" t="n">
-        <v>3.018</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1434</v>
+        <v>-0.2643</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1401</v>
+        <v>0.1573</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.0033</v>
+        <v>-0.4216</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.3917</v>
+        <v>0.4639</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.7581</v>
+        <v>-0.3539</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9709</v>
+        <v>0.118</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7872</v>
+        <v>-0.4718</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. SAMODUROV</t>
+          <t>J. HERNANGOMEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.0049</v>
+        <v>-1.7627</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.7327</v>
+        <v>-1.9651</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2722</v>
+        <v>0.2025</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.997</v>
+        <v>-1.2555</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1741</v>
+        <v>0.6785</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.1711</v>
+        <v>-1.9341</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.7327</v>
+        <v>-1.423</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0168</v>
+        <v>0.5581</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.7495000000000001</v>
+        <v>-1.9811</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.2643</v>
+        <v>0.1675</v>
       </c>
       <c r="N23" t="n">
-        <v>0.1573</v>
+        <v>0.1205</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.4216</v>
+        <v>0.047</v>
       </c>
       <c r="P23" t="n">
-        <v>0.4639</v>
+        <v>1.6237</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.4639</v>
+        <v>1.6237</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4718</v>
+        <v>0.0136</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>-0.5421</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4718</v>
+        <v>0.5557</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="24">
@@ -2359,19 +2359,19 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>9.5848</v>
+        <v>9.5847</v>
       </c>
       <c r="E25" t="n">
-        <v>10.7349</v>
+        <v>10.7348</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.1499</v>
+        <v>-1.1498</v>
       </c>
       <c r="G25" t="n">
         <v>9.292699999999998</v>
       </c>
       <c r="H25" t="n">
-        <v>7.184899999999997</v>
+        <v>7.184899999999999</v>
       </c>
       <c r="I25" t="n">
         <v>2.1077</v>
@@ -2389,7 +2389,7 @@
         <v>-2.1646</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.2916</v>
+        <v>-0.2916000000000001</v>
       </c>
       <c r="O25" t="n">
         <v>-1.873</v>
@@ -2404,7 +2404,7 @@
         <v>10.4379</v>
       </c>
       <c r="S25" t="n">
-        <v>-4.7181</v>
+        <v>-4.718100000000001</v>
       </c>
       <c r="T25" t="n">
         <v>-3.084</v>
